--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_o_higgins.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:51</t>
+    <t xml:space="preserve">2026-09-24 00:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -926,16 +926,16 @@
         <v>-0.75</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>-0.77</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>26</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
@@ -972,13 +972,13 @@
         <v>-0.87</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>-0.66</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.21</v>
@@ -992,19 +992,19 @@
         <v>26</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.82</v>
+        <v>-0.8</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.41</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="22">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_o_higgins.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:42</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_o_higgins.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
